--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_5_R1.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_5_R1.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6985</v>
+        <v>6.2083</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8042</v>
+        <v>7.5992</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8943</v>
+        <v>-1.3909</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3394</v>
+        <v>0.3516</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8579</v>
+        <v>-2.9542</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5185</v>
+        <v>3.3058</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5011</v>
+        <v>1.7137</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2802</v>
+        <v>-2.1742</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2208</v>
+        <v>3.8879</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1617</v>
+        <v>-1.3621</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4223</v>
+        <v>-0.78</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.5821</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8773</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4629</v>
+        <v>-0.0116</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5856</v>
+        <v>-0.9566</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1418</v>
+        <v>5.8971</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>5.8971</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7536</v>
+        <v>5.6945</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2453</v>
+        <v>4.6993</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4917</v>
+        <v>0.9951</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3516</v>
+        <v>4.3394</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.9542</v>
+        <v>4.8579</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3058</v>
+        <v>-0.5185</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7137</v>
+        <v>5.5011</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.1742</v>
+        <v>5.2802</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8879</v>
+        <v>0.2208</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3621</v>
+        <v>-1.1617</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.78</v>
+        <v>-0.4223</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5821</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9278</v>
+        <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4229</v>
+        <v>-0.1267</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3655</v>
+        <v>0.358</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0574</v>
+        <v>-0.4848</v>
       </c>
       <c r="V3" t="n">
-        <v>5.8971</v>
+        <v>-0.1418</v>
       </c>
       <c r="W3" t="n">
-        <v>5.8971</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.999</v>
+        <v>2.9044</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2554</v>
+        <v>1.8583</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7436</v>
+        <v>1.0461</v>
       </c>
       <c r="G4" t="n">
         <v>1.1392</v>
@@ -766,13 +766,13 @@
         <v>2.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3238</v>
+        <v>0.2291</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8338</v>
+        <v>0.4367</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.51</v>
+        <v>-0.2076</v>
       </c>
       <c r="V4" t="n">
         <v>1.0722</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1222</v>
+        <v>2.585</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4322</v>
+        <v>3.0966</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.31</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>4.0563</v>
@@ -844,13 +844,13 @@
         <v>3.0154</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5578</v>
+        <v>-1.095</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0455</v>
+        <v>-0.3811</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5122</v>
+        <v>-0.7139</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>T. GINAT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1177</v>
+        <v>0.2004</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0672</v>
+        <v>-0.2544</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.185</v>
+        <v>0.4548</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3722</v>
+        <v>0.4747</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1642</v>
+        <v>-0.2581</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2079</v>
+        <v>0.7328</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3264</v>
+        <v>0.575</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1091</v>
+        <v>-0.1611</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2173</v>
+        <v>0.7361</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6986</v>
+        <v>-0.1003</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2734</v>
+        <v>-0.097</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4252</v>
+        <v>-0.0033</v>
       </c>
       <c r="P6" t="n">
-        <v>2.7834</v>
+        <v>-0.232</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7834</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.315</v>
+        <v>-0.0424</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2592</v>
+        <v>0.3304</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0558</v>
+        <v>-0.3727</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.168</v>
+        <v>0.0174</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1.3031</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.168</v>
+        <v>-1.2858</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.168</v>
+        <v>-1.3722</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.168</v>
+        <v>-0.1642</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-1.2079</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.3264</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.1091</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.2173</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.168</v>
+        <v>-2.6986</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.168</v>
+        <v>-1.2734</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.4252</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.7834</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.1799</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.0233</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.1566</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. GINAT</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2453</v>
+        <v>-0.168</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8008999999999999</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5556</v>
+        <v>-0.168</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4747</v>
+        <v>-0.168</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2581</v>
+        <v>-0.168</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7328</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.575</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1611</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7361</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1003</v>
+        <v>-0.168</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.097</v>
+        <v>-0.168</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0033</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4881</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2161</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2719</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8321</v>
+        <v>-1.3032</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.4592</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5272</v>
+        <v>-1.7624</v>
       </c>
       <c r="G9" t="n">
         <v>0.0342</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2754</v>
+        <v>-0.1957</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4955</v>
+        <v>0.2596</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2201</v>
+        <v>-0.4553</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6778999999999999</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7828</v>
+        <v>-1.429</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7758</v>
+        <v>-1.4219</v>
       </c>
       <c r="F10" t="n">
         <v>-0.0071</v>
@@ -1234,10 +1234,10 @@
         <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3407</v>
+        <v>-0.9869</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5895</v>
+        <v>-0.2357</v>
       </c>
       <c r="U10" t="n">
         <v>-0.7512</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.974</v>
+        <v>-1.8828</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3252</v>
+        <v>0.2819</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2991</v>
+        <v>-2.1647</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2416</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2838</v>
+        <v>-0.1926</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0395</v>
+        <v>-0.0037</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3233</v>
+        <v>-0.1889</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1444</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.4534</v>
+        <v>12.827</v>
       </c>
       <c r="E12" t="n">
-        <v>17.2479</v>
+        <v>17.6213</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.7946</v>
+        <v>-4.794499999999999</v>
       </c>
       <c r="G12" t="n">
         <v>11.1869</v>
@@ -1381,7 +1381,7 @@
         <v>-6.6073</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4793</v>
+        <v>3.479299999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.9172</v>
@@ -1390,13 +1390,13 @@
         <v>17.3964</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.9318</v>
+        <v>-3.5583</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3559</v>
+        <v>0.7292999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.2875</v>
+        <v>-4.2876</v>
       </c>
       <c r="V12" t="n">
         <v>1.719</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.8462</v>
+        <v>7.5101</v>
       </c>
       <c r="E13" t="n">
         <v>7.1496</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6966</v>
+        <v>0.3606</v>
       </c>
       <c r="G13" t="n">
         <v>3.5554</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1464</v>
+        <v>1.8104</v>
       </c>
       <c r="T13" t="n">
         <v>0.9006</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2459</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>2.1444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7442</v>
+        <v>1.6821</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2741</v>
+        <v>1.9202</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5299</v>
+        <v>-0.2382</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3691</v>
@@ -1546,13 +1546,13 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3453</v>
+        <v>0.2831</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5702</v>
+        <v>0.2164</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2249</v>
+        <v>0.0668</v>
       </c>
       <c r="V14" t="n">
         <v>1.0722</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0586</v>
+        <v>0.1355</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0147</v>
+        <v>0.0098</v>
       </c>
       <c r="F15" t="n">
-        <v>0.044</v>
+        <v>0.1258</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1512</v>
+        <v>-2.123</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4561</v>
+        <v>-2.1764</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3049</v>
+        <v>0.0534</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2813</v>
+        <v>-0.3394</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7427</v>
+        <v>-1.8682</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5386</v>
+        <v>1.5289</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1302</v>
+        <v>-1.7837</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2866</v>
+        <v>-0.3082</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8435</v>
+        <v>-1.4755</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.7112</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.1029</v>
+        <v>-1.6237</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6187</v>
+        <v>1.1863</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8363</v>
+        <v>0.9006</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7824</v>
+        <v>0.2858</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0112</v>
+        <v>-0.0621</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1415</v>
+        <v>-0.6584</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1303</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.0569</v>
+        <v>-1.457</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3108</v>
+        <v>-1.2496</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7461</v>
+        <v>-0.2074</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5525</v>
+        <v>-0.5919</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08749999999999999</v>
+        <v>-0.7023</v>
       </c>
       <c r="L16" t="n">
-        <v>0.465</v>
+        <v>0.1104</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6095</v>
+        <v>-0.8651</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3983</v>
+        <v>-0.5473</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2112</v>
+        <v>-0.3178</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R16" t="n">
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9959</v>
+        <v>0.0934</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9085</v>
+        <v>0.0237</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0696</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3659</v>
+        <v>-0.7664</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1302</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7643</v>
+        <v>-0.1913</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.457</v>
+        <v>1.1512</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2496</v>
+        <v>2.4561</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2074</v>
+        <v>-1.3049</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5919</v>
+        <v>3.2813</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7023</v>
+        <v>2.7427</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1104</v>
+        <v>0.5386</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8651</v>
+        <v>-2.1302</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5473</v>
+        <v>-0.2866</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3178</v>
+        <v>-1.8435</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.232</v>
+        <v>-5.1029</v>
       </c>
       <c r="R17" t="n">
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2104</v>
+        <v>1.7937</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4481</v>
+        <v>1.2465</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2377</v>
+        <v>0.5472</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3686</v>
+        <v>-1.0269</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0098</v>
+        <v>0.3158</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3783</v>
+        <v>-1.3427</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.123</v>
+        <v>-2.0569</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.1764</v>
+        <v>-1.3108</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0534</v>
+        <v>-0.7461</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3394</v>
+        <v>0.5525</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.8682</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5289</v>
+        <v>0.465</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7837</v>
+        <v>-2.6095</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3082</v>
+        <v>-1.3983</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4755</v>
+        <v>-1.2112</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.6237</v>
+        <v>-1.3917</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6822</v>
+        <v>-0.0422</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9006</v>
+        <v>0.0828</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2183</v>
+        <v>-0.125</v>
       </c>
       <c r="V18" t="n">
         <v>1.0722</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7607</v>
+        <v>-1.256</v>
       </c>
       <c r="E19" t="n">
-        <v>0.867</v>
+        <v>1.1029</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6278</v>
+        <v>-2.3589</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2523</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1863</v>
+        <v>0.3185</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2636</v>
+        <v>0.4995</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4498</v>
+        <v>-0.181</v>
       </c>
       <c r="V19" t="n">
         <v>0.1418</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2735</v>
+        <v>-2.0376</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0307</v>
+        <v>-0.7948</v>
       </c>
       <c r="F20" t="n">
         <v>-1.2427</v>
@@ -2014,10 +2014,10 @@
         <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>1.317</v>
+        <v>1.5529</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9085</v>
+        <v>1.1444</v>
       </c>
       <c r="U20" t="n">
         <v>0.4086</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8512</v>
+        <v>-4.2728</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3051</v>
+        <v>-0.9513</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.546</v>
+        <v>-3.3216</v>
       </c>
       <c r="G22" t="n">
         <v>-3.525</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4137</v>
+        <v>-0.8353</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5149</v>
+        <v>-0.161</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8988</v>
+        <v>-0.6743</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9361</v>
+        <v>-4.4421</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3697</v>
+        <v>-0.1338</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.5664</v>
+        <v>-4.3083</v>
       </c>
       <c r="G23" t="n">
         <v>-1.483</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0767</v>
+        <v>-0.5827</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5149</v>
+        <v>-0.279</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5619</v>
+        <v>-0.3038</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1444</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9535</v>
+        <v>-4.5267</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4304</v>
+        <v>-1.1945</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5231</v>
+        <v>-3.3322</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6848</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0548</v>
+        <v>-0.628</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6067</v>
+        <v>-0.4158</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7501</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.4536</v>
+        <v>-11.6672</v>
       </c>
       <c r="E25" t="n">
-        <v>4.7946</v>
+        <v>4.794400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-17.2479</v>
+        <v>-16.4615</v>
       </c>
       <c r="G25" t="n">
         <v>-11.1867</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.5208</v>
+        <v>-2.520799999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-8.666200000000002</v>
@@ -2404,13 +2404,13 @@
         <v>13.9172</v>
       </c>
       <c r="S25" t="n">
-        <v>3.9316</v>
+        <v>4.7181</v>
       </c>
       <c r="T25" t="n">
         <v>4.2876</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3557</v>
+        <v>0.4306000000000003</v>
       </c>
       <c r="V25" t="n">
         <v>-1.719</v>
